--- a/data/trans_bre/P32-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P32-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 4,64</t>
+          <t>-5,32; 4,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,66; -8,8</t>
+          <t>-27,06; -9,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 1,59</t>
+          <t>-15,34; 0,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,9; -1,77</t>
+          <t>-10,82; -1,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 316,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,23; -29,2</t>
+          <t>-93,65; -37,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 19,9</t>
+          <t>-76,67; 22,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,09</t>
+          <t>-7,95; 0,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,61; -2,26</t>
+          <t>-10,37; -1,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,54</t>
+          <t>-1,97; 4,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,5</t>
+          <t>-3,9; 0,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,12</t>
+          <t>-100,0; 62,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,83; -20,91</t>
+          <t>-91,51; -14,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,35</t>
+          <t>-3,84; 1,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,74</t>
+          <t>-4,02; 0,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -3,06</t>
+          <t>-12,85; -2,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-93,43; -33,41</t>
+          <t>-93,67; -23,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,66</t>
+          <t>-5,39; 3,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 2,65</t>
+          <t>-6,32; 2,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,36</t>
+          <t>-5,7; 1,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -1,14</t>
+          <t>-8,85; -1,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,21; 133,78</t>
+          <t>-84,77; 137,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 118,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 119,11</t>
+          <t>-100,0; 186,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,15</t>
+          <t>-100,0; -21,49</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 14,99</t>
+          <t>-3,6; 13,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,42; -1,29</t>
+          <t>-13,05; -1,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,84; -1,02</t>
+          <t>-8,74; -1,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,27</t>
+          <t>-100,0; 13,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 2,63</t>
+          <t>-3,88; 2,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 0,72</t>
+          <t>-5,51; 1,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,09</t>
+          <t>-3,78; 3,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 0,56</t>
+          <t>-7,96; 0,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-93,43; 42,64</t>
+          <t>-89,5; 58,7</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -0,62</t>
+          <t>-4,17; -0,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,62</t>
+          <t>-6,34; -0,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 1,85</t>
+          <t>-7,67; 2,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,48; -4,16</t>
+          <t>-18,87; -4,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 3,98</t>
+          <t>-93,46; -1,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-61,27; 26,69</t>
+          <t>-61,07; 29,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-94,54; -28,44</t>
+          <t>-95,53; -31,9</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,89</t>
+          <t>-2,45; 0,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,98</t>
+          <t>-4,94; 0,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,63</t>
+          <t>-3,52; 1,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 6,18</t>
+          <t>-1,93; 5,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 212,39</t>
+          <t>-100,0; 184,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,24; 48,96</t>
+          <t>-89,04; 49,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-89,3; 51,57</t>
+          <t>-89,62; 57,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-70,78; 527,78</t>
+          <t>-74,27; 500,08</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,07</t>
+          <t>-2,35; -0,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -2,87</t>
+          <t>-6,12; -3,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,61</t>
+          <t>-3,37; -0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -1,92</t>
+          <t>-5,85; -2,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 2,35</t>
+          <t>-73,81; -4,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-80,37; -46,23</t>
+          <t>-81,63; -51,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-56,58; -10,58</t>
+          <t>-57,76; -9,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-81,51; -35,92</t>
+          <t>-81,43; -38,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P32-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,77</t>
+          <t>-4,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 4,2</t>
+          <t>-5,15; 4,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,06; -9,02</t>
+          <t>-26,29; -8,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 0,88</t>
+          <t>-15,46; 0,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -1,84</t>
+          <t>-9,01; -1,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 316,76</t>
+          <t>-100,0; 472,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,65; -37,67</t>
+          <t>-93,44; -32,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,67; 22,37</t>
+          <t>-79,59; 11,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-69,15%</t>
+          <t>-69,46%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,17</t>
+          <t>-8,17; 0,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,37; -1,79</t>
+          <t>-10,2; -1,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 4,18</t>
+          <t>-2,13; 3,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,53</t>
+          <t>-3,8; 0,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 62,48</t>
+          <t>-100,0; 48,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,51; -14,29</t>
+          <t>-92,49; -14,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,61</t>
+          <t>-10,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-75,36%</t>
+          <t>-79,7%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-2,89; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,12</t>
+          <t>-3,77; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,63</t>
+          <t>-4,09; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -2,89</t>
+          <t>-16,31; -4,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-93,67; -23,39</t>
+          <t>-95,13; -43,25</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-84,48%</t>
+          <t>-83,33%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,59</t>
+          <t>-5,08; 4,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 2,01</t>
+          <t>-6,25; 2,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 1,74</t>
+          <t>-5,97; 1,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -1,39</t>
+          <t>-7,87; -1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,77; 137,69</t>
+          <t>-82,9; 200,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 118,89</t>
+          <t>-100,0; 209,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 186,58</t>
+          <t>-100,0; 107,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -21,49</t>
+          <t>-100,0; -18,27</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 13,04</t>
+          <t>-3,64; 13,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; -1,08</t>
+          <t>-12,81; -0,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,74; -1,03</t>
+          <t>-8,67; -1,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,85</t>
+          <t>-100,0; 36,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-2,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-57,89%</t>
+          <t>-48,85%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,67</t>
+          <t>-3,86; 2,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,06</t>
+          <t>-6,31; 0,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,1</t>
+          <t>-3,56; 3,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 0,56</t>
+          <t>-7,14; 1,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 448,87</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,5; 58,7</t>
+          <t>-90,67; 62,47</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-9,95</t>
+          <t>-5,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-73,2%</t>
+          <t>-38,94%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,62</t>
+          <t>-4,1; -0,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -0,93</t>
+          <t>-6,46; -0,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 2,05</t>
+          <t>-7,07; 1,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -4,18</t>
+          <t>-11,6; 0,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-93,46; -1,16</t>
+          <t>-94,05; 7,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 29,34</t>
+          <t>-58,73; 30,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -31,9</t>
+          <t>-67,49; 8,11</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,94</t>
+          <t>-2,33; 0,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 0,92</t>
+          <t>-5,23; 0,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,04</t>
+          <t>-3,51; 0,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 5,78</t>
+          <t>-1,94; 5,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 184,53</t>
+          <t>-100,0; 309,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,04; 49,65</t>
+          <t>-90,88; 45,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 57,34</t>
+          <t>-87,56; 58,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,27; 500,08</t>
+          <t>-71,58; 626,89</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-61,46%</t>
+          <t>-46,92%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -0,16</t>
+          <t>-2,36; -0,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -3,12</t>
+          <t>-6,2; -3,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,4</t>
+          <t>-3,52; -0,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -2,04</t>
+          <t>-4,72; -1,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-73,81; -4,48</t>
+          <t>-71,69; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-81,63; -51,27</t>
+          <t>-81,97; -50,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-57,76; -9,03</t>
+          <t>-57,61; -8,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-81,43; -38,19</t>
+          <t>-64,6; -15,54</t>
         </is>
       </c>
     </row>
